--- a/result/CCND2_LUSC_Tables.xlsx
+++ b/result/CCND2_LUSC_Tables.xlsx
@@ -1745,7 +1745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1778,21 +1778,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>ageG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.021</v>
+        <v>1.319</v>
       </c>
       <c r="C2" t="n">
-        <v>1.002</v>
+        <v>0.957</v>
       </c>
       <c r="D2" t="n">
-        <v>1.041</v>
+        <v>1.817</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>0.090</t>
         </is>
       </c>
     </row>
@@ -1803,227 +1803,80 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.996</v>
+        <v>0.995</v>
       </c>
       <c r="D3" t="n">
         <v>1.005</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>0.997</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>pathologic_stage</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>1.202</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>1.003</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.794</t>
+          <t>0.046</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDKN2AExpression</t>
+          <t>CCND2group_Low</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>1.354</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>1.007</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.822</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.828</t>
+          <t>0.045</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SOX2Expression</t>
+          <t>gender_MALE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>1.249</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.883</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.767</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.119</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>PIK3CAExpression</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.329</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NOTCH1Expression</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.945</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CCND2group_Low</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.397</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.028</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.032</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>gender_MALE</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.255</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.799</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.217</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>pathologic_stage_2.0</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.083</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.545</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.659</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>pathologic_stage_3.0</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.424</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.953</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2.126</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.084</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>pathologic_stage_4.0</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.204</v>
-      </c>
-      <c r="D13" t="n">
-        <v>7.627</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0.019</t>
+          <t>0.208</t>
         </is>
       </c>
     </row>
